--- a/web/files/九龙-何文田-st. george's mansions.xlsx
+++ b/web/files/九龙-何文田-st. george's mansions.xlsx
@@ -4951,23 +4951,19 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>29270000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>38312</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4976,12 +4972,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -4991,7 +4987,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13131,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -13145,7 +13141,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13258,12 +13254,12 @@
 (24年-11月-04日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
+$2927万
+$38,312/呎
+(26年-09月-16日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-st. george's mansions.xlsx
+++ b/web/files/九龙-何文田-st. george's mansions.xlsx
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2141</v>
+        <v>2024</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>120180000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>56133</v>
+        <v>59377</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>764</v>
+        <v>723</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4758,14 +4758,14 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
         <v>29680000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>38848</v>
+        <v>41051</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -12541,9 +12541,9 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 2141呎 (4+房)
+          <t>A | 2024呎 (4+房)
 $12018万
-$56,133/呎
+$59,377/呎
 (23年-04月-17日)</t>
         </is>
       </c>
@@ -13225,10 +13225,10 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 764呎 (2房)
+          <t>C | 723呎 (2房)
 $2968万
-$38,848/呎
-(26年-09月-01日)</t>
+$41,051/呎
+(26年-09月-21日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-st. george's mansions.xlsx
+++ b/web/files/九龙-何文田-st. george's mansions.xlsx
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>764</v>
+        <v>723</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4956,14 +4956,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
         <v>29270000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38312</v>
+        <v>40484</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 764呎 (2房)
+          <t>C | 723呎 (2房)
 $2927万
-$38,312/呎
-(26年-09月-16日)</t>
+$40,484/呎
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-何文田-st. george's mansions.xlsx
+++ b/web/files/九龙-何文田-st. george's mansions.xlsx
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>26740000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>37036</v>
+        <v>35000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>26200000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>36288</v>
+        <v>34293</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>27050000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>37465</v>
+        <v>35406</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1725</v>
+        <v>1842</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>92100000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>53391</v>
+        <v>50000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2024</v>
+        <v>2141</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>120180000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>59377</v>
+        <v>56133</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>24661000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>34157</v>
+        <v>32279</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>88000000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>51044</v>
+        <v>47800</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2024</v>
+        <v>2140</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>119000000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>58794</v>
+        <v>55607</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>86000000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>49884</v>
+        <v>46714</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2024</v>
+        <v>2140</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>118000000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>58300</v>
+        <v>55140</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>23820000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>32992</v>
+        <v>31178</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>85000000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>49304</v>
+        <v>46171</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>23400000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>32410</v>
+        <v>30628</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>83800000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>48608</v>
+        <v>45519</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>24628000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>34111</v>
+        <v>32236</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>82800000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>48028</v>
+        <v>44976</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>25100000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>34765</v>
+        <v>32853</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>22220000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>30776</v>
+        <v>29084</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>82740000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>47993</v>
+        <v>44943</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>79500000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>46114</v>
+        <v>43183</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>21782000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>30169</v>
+        <v>28510</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>78380000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>45464</v>
+        <v>42575</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>21500000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>29778</v>
+        <v>28141</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>22770000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>31537</v>
+        <v>29804</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>83000000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>48144</v>
+        <v>45084</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2024</v>
+        <v>2140</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>96800000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>47826</v>
+        <v>45234</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>22540000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>31219</v>
+        <v>29503</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1724</v>
+        <v>1841</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>69000000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>40023</v>
+        <v>37480</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2024</v>
+        <v>2140</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>89000000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>43972</v>
+        <v>41589</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1725</v>
+        <v>1842</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>70300000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>40754</v>
+        <v>38165</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2024</v>
+        <v>2141</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>93000000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>45949</v>
+        <v>43438</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>722</v>
+        <v>764</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>22470000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>31122</v>
+        <v>29411</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1725</v>
+        <v>1842</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>68080000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>39467</v>
+        <v>36960</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>3559</v>
+        <v>3695</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>260000000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>73054</v>
+        <v>70365</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>29680000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>41051</v>
+        <v>38848</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1752</v>
+        <v>1869</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>90130000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>51444</v>
+        <v>48224</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>29270000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>40484</v>
+        <v>38312</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1752</v>
+        <v>1869</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>177650000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>101398</v>
+        <v>95051</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1755</v>
+        <v>1871</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>177650000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>101225</v>
+        <v>94949</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1752</v>
+        <v>1869</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>86900000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>49600</v>
+        <v>46495</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1755</v>
+        <v>1871</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>86900000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>49516</v>
+        <v>46446</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         <v>24663000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>34112</v>
+        <v>32281</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>93880000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>53584</v>
+        <v>50257</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>24174000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>33436</v>
+        <v>31641</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>85500000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>48801</v>
+        <v>45771</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>84500000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>48148</v>
+        <v>45187</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>86750000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>49515</v>
+        <v>46440</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>85750000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>48860</v>
+        <v>45856</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>23447160</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>32430</v>
+        <v>30690</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>82500000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>47089</v>
+        <v>44165</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>81490000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>46433</v>
+        <v>43578</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>22800000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>31535</v>
+        <v>29843</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
         <v>95000000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>54224</v>
+        <v>50857</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>88000000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>50142</v>
+        <v>47059</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>22580000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>31231</v>
+        <v>29555</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>87260000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>49806</v>
+        <v>46713</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>86350000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>49202</v>
+        <v>46176</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>81400000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>46461</v>
+        <v>43576</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>22660000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>31342</v>
+        <v>29660</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>23520000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>32531</v>
+        <v>30785</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>83000000</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>47293</v>
+        <v>44385</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>23220000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>32116</v>
+        <v>30393</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>81400000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>46461</v>
+        <v>43576</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>1755</v>
+        <v>1870</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>88080000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>50188</v>
+        <v>47102</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>21850000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>30221</v>
+        <v>28599</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>75800000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>43265</v>
+        <v>40578</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>1752</v>
+        <v>1868</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>68000000</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>38813</v>
+        <v>36403</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>26210000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>36252</v>
+        <v>34306</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>1752</v>
+        <v>1869</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>66600000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>38014</v>
+        <v>35634</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1755</v>
+        <v>1871</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>65000000</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>37037</v>
+        <v>34741</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>22470000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>31079</v>
+        <v>29411</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>1752</v>
+        <v>1869</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>68000000</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>38813</v>
+        <v>36383</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>1755</v>
+        <v>1871</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>66000000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>37607</v>
+        <v>35275</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>27020000</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>36913</v>
+        <v>35000</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>26479600</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>36174</v>
+        <v>34300</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>28540000</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>38989</v>
+        <v>36969</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>25180000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>34399</v>
+        <v>32617</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>1973</v>
+        <v>2087</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>113000000</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>57273</v>
+        <v>54145</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>24747000</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>33807</v>
+        <v>32056</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>81253000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>47185</v>
+        <v>44183</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>98680000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>50041</v>
+        <v>47283</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>24310000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>33210</v>
+        <v>31490</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>80000000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>46458</v>
+        <v>43502</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>98000000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>49696</v>
+        <v>46957</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>23950000</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>32719</v>
+        <v>31023</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>78500000</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>45587</v>
+        <v>42686</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>95687700</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>48523</v>
+        <v>45849</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>23570000</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>32199</v>
+        <v>30531</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>76900000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>44657</v>
+        <v>41816</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>94800000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>48073</v>
+        <v>45424</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>23500000</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>32104</v>
+        <v>30440</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>75800000</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>44019</v>
+        <v>41218</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>91000000</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>46146</v>
+        <v>43603</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>23150000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>31626</v>
+        <v>29987</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>74800000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>43438</v>
+        <v>40674</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>89000000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>42625</v>
+        <v>42645</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>22800000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>31148</v>
+        <v>29534</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>74000000</v>
       </c>
       <c r="I149" s="5" t="n">
-        <v>42973</v>
+        <v>40239</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>88500000</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>44878</v>
+        <v>42405</v>
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>24250000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>33128</v>
+        <v>31412</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>73600000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>42741</v>
+        <v>40022</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>88000000</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>44625</v>
+        <v>42166</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>27380000</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>37404</v>
+        <v>35466</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>72880000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>42323</v>
+        <v>39630</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>87380000</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>44310</v>
+        <v>41869</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>21750000</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>29713</v>
+        <v>28174</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>72000000</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>41812</v>
+        <v>39152</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>86380000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>43803</v>
+        <v>41390</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>21400000</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>29235</v>
+        <v>27720</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>70000000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>40650</v>
+        <v>38064</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>85480000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>43347</v>
+        <v>40958</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>26620000</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>36366</v>
+        <v>34482</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>72450000</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>42073</v>
+        <v>39396</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>83500000</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>42343</v>
+        <v>40010</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>22650000</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>30943</v>
+        <v>29339</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>67500000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>39199</v>
+        <v>36705</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>80200000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>40669</v>
+        <v>38428</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>20760000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>28361</v>
+        <v>26891</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>1722</v>
+        <v>1839</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>65200000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>37863</v>
+        <v>35454</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1972</v>
+        <v>2087</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>77800000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>39452</v>
+        <v>37278</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>732</v>
+        <v>772</v>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         <v>20550000</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>28074</v>
+        <v>26619</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1723</v>
+        <v>1840</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>63800000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>37028</v>
+        <v>34674</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>1973</v>
+        <v>2087</v>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>76280000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>38662</v>
+        <v>36550</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1723</v>
+        <v>1840</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>64500000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>37435</v>
+        <v>35054</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>1973</v>
+        <v>2087</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>78000000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>39534</v>
+        <v>37374</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -12471,9 +12471,9 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2674万
-$37,036/呎
+$35,000/呎
 (24年-09月-11日)</t>
         </is>
       </c>
@@ -12495,9 +12495,9 @@
       <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2620万
-$36,288/呎
+$34,293/呎
 (25年-10月-31日)</t>
         </is>
       </c>
@@ -12541,25 +12541,25 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2141呎 (4+房)
 $12018万
-$59,377/呎
+$56,133/呎
 (23年-04月-17日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1725呎 (3房)
+          <t>B | 1842呎 (3房)
 $9210万
-$53,391/呎
+$50,000/呎
 (25年-08月-06日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2705万
-$37,465/呎
+$35,406/呎
 (26年-06月-10日)</t>
         </is>
       </c>
@@ -12572,25 +12572,25 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2140呎 (4+房)
 $11900万
-$58,794/呎
+$55,607/呎
 (23年-03月-30日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8800万
-$51,044/呎
+$47,800/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2466万
-$34,157/呎
+$32,279/呎
 (24年-11月-14日)</t>
         </is>
       </c>
@@ -12603,17 +12603,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2140呎 (4+房)
 $11800万
-$58,300/呎
+$55,140/呎
 (24年-11月-13日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8600万
-$49,884/呎
+$46,714/呎
 (25年-05月-14日)</t>
         </is>
       </c>
@@ -12642,17 +12642,17 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8500万
-$49,304/呎
+$46,171/呎
 (25年-02月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2382万
-$32,992/呎
+$31,178/呎
 (25年-06月-02日)</t>
         </is>
       </c>
@@ -12681,9 +12681,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2340万
-$32,410/呎
+$30,628/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -12704,9 +12704,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8380万
-$48,608/呎
+$45,519/呎
 (25年-01月-10日)</t>
         </is>
       </c>
@@ -12735,17 +12735,17 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8280万
-$48,028/呎
+$44,976/呎
 (25年-03月-13日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2463万
-$34,111/呎
+$32,236/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -12774,9 +12774,9 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2510万
-$34,765/呎
+$32,853/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -12797,17 +12797,17 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8274万
-$47,993/呎
+$44,943/呎
 (25年-07月-22日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2222万
-$30,776/呎
+$29,084/呎
 (25年-11月-06日)</t>
         </is>
       </c>
@@ -12828,9 +12828,9 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $7950万
-$46,114/呎
+$43,183/呎
 (25年-06月-20日)</t>
         </is>
       </c>
@@ -12859,17 +12859,17 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $7838万
-$45,464/呎
+$42,575/呎
 (25年-06月-20日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2178万
-$30,169/呎
+$28,510/呎
 (24年-12月-06日)</t>
         </is>
       </c>
@@ -12898,9 +12898,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2150万
-$29,778/呎
+$28,141/呎
 (24年-11月-06日)</t>
         </is>
       </c>
@@ -12944,25 +12944,25 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2140呎 (4+房)
 $9680万
-$47,826/呎
+$45,234/呎
 (23年-08月-29日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $8300万
-$48,144/呎
+$45,084/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2277万
-$31,537/呎
+$29,804/呎
 (26年-07月-02日)</t>
         </is>
       </c>
@@ -12975,25 +12975,25 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2140呎 (4+房)
 $8900万
-$43,972/呎
+$41,589/呎
 (23年-12月-06日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1724呎 (3房)
+          <t>B | 1841呎 (3房)
 $6900万
-$40,023/呎
+$37,480/呎
 (25年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2254万
-$31,219/呎
+$29,503/呎
 (26年-06月-17日)</t>
         </is>
       </c>
@@ -13006,17 +13006,17 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 2024呎 (4+房)
+          <t>A | 2141呎 (4+房)
 $9300万
-$45,949/呎
+$43,438/呎
 (26年-08月-12日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1725呎 (3房)
+          <t>B | 1842呎 (3房)
 $7030万
-$40,754/呎
+$38,165/呎
 (25年-10月-27日)</t>
         </is>
       </c>
@@ -13045,17 +13045,17 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1725呎 (3房)
+          <t>B | 1842呎 (3房)
 $6808万
-$39,467/呎
+$36,960/呎
 (25年-02月-18日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 722呎 (2房)
+          <t>C | 764呎 (2房)
 $2247万
-$31,122/呎
+$29,411/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -13185,9 +13185,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3559呎 (4+房)
+          <t>A | 3695呎 (4+房)
 $26000万
-$73,054/呎
+$70,365/呎
 (21年-06月-30日)</t>
         </is>
       </c>
@@ -13217,17 +13217,17 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1869呎 (3房)
 $9013万
-$51,444/呎
+$48,224/呎
 (24年-11月-28日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2968万
-$41,051/呎
+$38,848/呎
 (26年-09月-21日)</t>
         </is>
       </c>
@@ -13240,25 +13240,25 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1871呎 (3房)
 $17765万
-$101,225/呎
+$94,949/呎
 (24年-11月-04日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1869呎 (3房)
 $17765万
-$101,398/呎
+$95,051/呎
 (24年-11月-04日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2927万
-$40,484/呎
+$38,312/呎
 (26年-10月-14日)</t>
         </is>
       </c>
@@ -13271,17 +13271,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1871呎 (3房)
 $8690万
-$49,516/呎
+$46,446/呎
 (24年-11月-29日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1869呎 (3房)
 $8690万
-$49,600/呎
+$46,495/呎
 (24年-11月-29日)</t>
         </is>
       </c>
@@ -13310,17 +13310,17 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $9388万
-$53,584/呎
+$50,257/呎
 (23年-02月-16日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2466万
-$34,112/呎
+$32,281/呎
 (25年-05月-28日)</t>
         </is>
       </c>
@@ -13333,25 +13333,25 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8450万
-$48,148/呎
+$45,187/呎
 (25年-02月-21日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8550万
-$48,801/呎
+$45,771/呎
 (25年-02月-21日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2417万
-$33,436/呎
+$31,641/呎
 (25年-02月-21日)</t>
         </is>
       </c>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8575万
-$48,860/呎
+$45,856/呎
 (25年-07月-10日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8675万
-$49,515/呎
+$46,440/呎
 (25年-07月-10日)</t>
         </is>
       </c>
@@ -13411,9 +13411,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2345万
-$32,430/呎
+$30,690/呎
 (24年-10月-10日)</t>
         </is>
       </c>
@@ -13426,17 +13426,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8149万
-$46,433/呎
+$43,578/呎
 (25年-05月-28日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8250万
-$47,089/呎
+$44,165/呎
 (25年-05月-28日)</t>
         </is>
       </c>
@@ -13457,25 +13457,25 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8800万
-$50,142/呎
+$47,059/呎
 (25年-09月-23日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $9500万
-$54,224/呎
+$50,857/呎
 (24年-07月-23日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2280万
-$31,535/呎
+$29,843/呎
 (24年-11月-27日)</t>
         </is>
       </c>
@@ -13488,25 +13488,25 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8635万
-$49,202/呎
+$46,176/呎
 (23年-02月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8726万
-$49,806/呎
+$46,713/呎
 (23年-02月-03日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2258万
-$31,231/呎
+$29,555/呎
 (25年-02月-07日)</t>
         </is>
       </c>
@@ -13527,9 +13527,9 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8140万
-$46,461/呎
+$43,576/呎
 (23年-03月-15日)</t>
         </is>
       </c>
@@ -13566,9 +13566,9 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2266万
-$31,342/呎
+$29,660/呎
 (25年-12月-17日)</t>
         </is>
       </c>
@@ -13581,9 +13581,9 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8300万
-$47,293/呎
+$44,385/呎
 (25年-10月-09日)</t>
         </is>
       </c>
@@ -13597,9 +13597,9 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2352万
-$32,531/呎
+$30,785/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -13628,9 +13628,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2322万
-$32,116/呎
+$30,393/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -13643,17 +13643,17 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1870呎 (3房)
 $8808万
-$50,188/呎
+$47,102/呎
 (26年-05月-19日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $8140万
-$46,461/呎
+$43,576/呎
 (24年-04月-17日)</t>
         </is>
       </c>
@@ -13682,17 +13682,17 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $7580万
-$43,265/呎
+$40,578/呎
 (25年-11月-12日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2185万
-$30,221/呎
+$28,599/呎
 (26年-02月-10日)</t>
         </is>
       </c>
@@ -13713,9 +13713,9 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1868呎 (3房)
 $6800万
-$38,813/呎
+$36,403/呎
 (25年-05月-28日)</t>
         </is>
       </c>
@@ -13736,25 +13736,25 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1871呎 (3房)
 $6500万
-$37,037/呎
+$34,741/呎
 (25年-05月-30日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1869呎 (3房)
 $6660万
-$38,014/呎
+$35,634/呎
 (25年-05月-28日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2621万
-$36,252/呎
+$34,306/呎
 (26年-08月-20日)</t>
         </is>
       </c>
@@ -13767,25 +13767,25 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1755呎 (3房)
+          <t>A | 1871呎 (3房)
 $6600万
-$37,607/呎
+$35,275/呎
 (25年-05月-19日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1752呎 (3房)
+          <t>B | 1869呎 (3房)
 $6800万
-$38,813/呎
+$36,383/呎
 (24年-11月-18日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 723呎 (2房)
+          <t>C | 764呎 (2房)
 $2247万
-$31,079/呎
+$29,411/呎
 (26年-02月-23日)</t>
         </is>
       </c>
@@ -13924,9 +13924,9 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2702万
-$36,913/呎
+$35,000/呎
 (24年-09月-12日)</t>
         </is>
       </c>
@@ -13948,9 +13948,9 @@
       <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2648万
-$36,174/呎
+$34,300/呎
 (24年-09月-12日)</t>
         </is>
       </c>
@@ -13979,9 +13979,9 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2854万
-$38,989/呎
+$36,969/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -13994,9 +13994,9 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 1973呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $11300万
-$57,273/呎
+$54,145/呎
 (23年-05月-10日)</t>
         </is>
       </c>
@@ -14010,9 +14010,9 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2518万
-$34,399/呎
+$32,617/呎
 (24年-11月-20日)</t>
         </is>
       </c>
@@ -14025,25 +14025,25 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $9868万
-$50,041/呎
+$47,283/呎
 (24年-10月-08日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $8125万
-$47,185/呎
+$44,183/呎
 (24年-12月-12日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2475万
-$33,807/呎
+$32,056/呎
 (24年-12月-12日)</t>
         </is>
       </c>
@@ -14056,25 +14056,25 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $9800万
-$49,696/呎
+$46,957/呎
 (24年-10月-31日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $8000万
-$46,458/呎
+$43,502/呎
 (24年-12月-12日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2431万
-$33,210/呎
+$31,490/呎
 (25年-09月-15日)</t>
         </is>
       </c>
@@ -14087,25 +14087,25 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $9569万
-$48,523/呎
+$45,849/呎
 (24年-06月-06日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7850万
-$45,587/呎
+$42,686/呎
 (25年-01月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2395万
-$32,719/呎
+$31,023/呎
 (25年-11月-21日)</t>
         </is>
       </c>
@@ -14118,25 +14118,25 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $9480万
-$48,073/呎
+$45,424/呎
 (24年-07月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7690万
-$44,657/呎
+$41,816/呎
 (24年-12月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2357万
-$32,199/呎
+$30,531/呎
 (25年-10月-10日)</t>
         </is>
       </c>
@@ -14149,25 +14149,25 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $9100万
-$46,146/呎
+$43,603/呎
 (24年-08月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7580万
-$44,019/呎
+$41,218/呎
 (24年-08月-27日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2350万
-$32,104/呎
+$30,440/呎
 (25年-01月-10日)</t>
         </is>
       </c>
@@ -14180,25 +14180,25 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 2088呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8900万
-$42,625/呎
+$42,645/呎
 (24年-11月-07日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7480万
-$43,438/呎
+$40,674/呎
 (24年-07月-31日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2315万
-$31,626/呎
+$29,987/呎
 (25年-09月-01日)</t>
         </is>
       </c>
@@ -14211,25 +14211,25 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8850万
-$44,878/呎
+$42,405/呎
 (24年-11月-01日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7400万
-$42,973/呎
+$40,239/呎
 (24年-11月-15日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2280万
-$31,148/呎
+$29,534/呎
 (25年-11月-24日)</t>
         </is>
       </c>
@@ -14242,25 +14242,25 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8800万
-$44,625/呎
+$42,166/呎
 (23年-12月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7360万
-$42,741/呎
+$40,022/呎
 (24年-12月-11日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2425万
-$33,128/呎
+$31,412/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -14273,25 +14273,25 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8738万
-$44,310/呎
+$41,869/呎
 (24年-11月-15日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7288万
-$42,323/呎
+$39,630/呎
 (24年-12月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2738万
-$37,404/呎
+$35,466/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -14304,25 +14304,25 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8638万
-$43,803/呎
+$41,390/呎
 (24年-08月-28日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7200万
-$41,812/呎
+$39,152/呎
 (24年-03月-12日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2175万
-$29,713/呎
+$28,174/呎
 (25年-11月-20日)</t>
         </is>
       </c>
@@ -14335,25 +14335,25 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8548万
-$43,347/呎
+$40,958/呎
 (24年-05月-14日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7000万
-$40,650/呎
+$38,064/呎
 (24年-07月-17日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2140万
-$29,235/呎
+$27,720/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -14366,25 +14366,25 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8350万
-$42,343/呎
+$40,010/呎
 (24年-08月-27日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $7245万
-$42,073/呎
+$39,396/呎
 (24年-04月-12日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2662万
-$36,366/呎
+$34,482/呎
 (26年-08月-17日)</t>
         </is>
       </c>
@@ -14397,25 +14397,25 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $8020万
-$40,669/呎
+$38,428/呎
 (25年-06月-19日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $6750万
-$39,199/呎
+$36,705/呎
 (24年-06月-18日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2265万
-$30,943/呎
+$29,339/呎
 (26年-06月-03日)</t>
         </is>
       </c>
@@ -14428,25 +14428,25 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 1972呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $7780万
-$39,452/呎
+$37,278/呎
 (24年-07月-08日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1722呎 (3房)
+          <t>B | 1839呎 (3房)
 $6520万
-$37,863/呎
+$35,454/呎
 (24年-07月-18日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2076万
-$28,361/呎
+$26,891/呎
 (25年-11月-27日)</t>
         </is>
       </c>
@@ -14459,25 +14459,25 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1973呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $7628万
-$38,662/呎
+$36,550/呎
 (24年-09月-05日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1723呎 (3房)
+          <t>B | 1840呎 (3房)
 $6380万
-$37,028/呎
+$34,674/呎
 (24年-05月-29日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 732呎 (2房)
+          <t>C | 772呎 (2房)
 $2055万
-$28,074/呎
+$26,619/呎
 (25年-02月-18日)</t>
         </is>
       </c>
@@ -14490,17 +14490,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1973呎 (4+房)
+          <t>A | 2087呎 (4+房)
 $7800万
-$39,534/呎
+$37,374/呎
 (24年-11月-14日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1723呎 (3房)
+          <t>B | 1840呎 (3房)
 $6450万
-$37,435/呎
+$35,054/呎
 (24年-10月-24日)</t>
         </is>
       </c>
